--- a/Spreadsheet Interface/Input_Spreadsheet_v250222.xlsx
+++ b/Spreadsheet Interface/Input_Spreadsheet_v250222.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kleinschmidtgroup-my.sharepoint.com/personal/kevin_nebiolo_kleinschmidtgroup_com/Documents/Software/stryke/Spreadsheet Interface/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_CDCAB5CB0247715E3683B1F3A2D225904E54B183" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BD7BF2A-9D1E-47E2-9079-362A8AAE7A60}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_CDCAB5CB0247715E3683B1F3A2D225904E54B183" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECFA113C-E7FF-462A-8B4A-56E2EA3B5A36}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Background and Metadata" sheetId="1" r:id="rId1"/>
@@ -26632,7 +26632,7 @@
         <v>0.4118</v>
       </c>
       <c r="L13">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="P13">
         <v>0.5907</v>
